--- a/artfynd/A 38132-2024 artfynd.xlsx
+++ b/artfynd/A 38132-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118169125</v>
+        <v>118169126</v>
       </c>
       <c r="B2" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Fisklösmossen, Lesjöfors, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455281</v>
+        <v>455179</v>
       </c>
       <c r="R2" t="n">
-        <v>6651363</v>
+        <v>6651199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118169126</v>
+        <v>118169125</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Fisklösmossen, Lesjöfors, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455179</v>
+        <v>455281</v>
       </c>
       <c r="R3" t="n">
-        <v>6651199</v>
+        <v>6651363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38132-2024 artfynd.xlsx
+++ b/artfynd/A 38132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118169126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,8 +881,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118169125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>